--- a/02_DIA_inicio_2026_analisis_assets/rbd_9433_escuela-basica-pablo-neruda_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9433_escuela-basica-pablo-neruda_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90528BC-FF10-4F77-97F7-9E4E2D913B13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BB7F88E-7605-4329-A39E-C2CA5C68A1D6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E837E8F3-607D-4327-9476-5D7FC03C086D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9D8BEED-2F27-41EA-AB15-0DA0AC70D7FB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC9F062B-D35A-4EC9-9761-A4899B1C944C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40D4734D-6121-449C-B10C-86899CCBED9B}"/>
 </file>